--- a/tests/TC-13/results/unscheduled_courses_even.xlsx
+++ b/tests/TC-13/results/unscheduled_courses_even.xlsx
@@ -637,12 +637,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>LEC, TUT</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Could not place combined LEC</t>
+          <t>Could not place combined LEC; Could not place combined TUT</t>
         </is>
       </c>
     </row>

--- a/tests/TC-13/results/unscheduled_courses_even.xlsx
+++ b/tests/TC-13/results/unscheduled_courses_even.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>DA151</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DA151</t>
+          <t>HS159</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HS159</t>
+          <t>EC155</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>EC155</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -612,19 +612,19 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>LEC, TUT</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Could not place combined LEC</t>
+          <t>Could not place combined LEC; Could not place combined TUT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>MA163</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -643,31 +643,6 @@
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Could not place combined LEC; Could not place combined TUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>MA163</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>CSE</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>LEC</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Could not place combined LEC</t>
         </is>
       </c>
     </row>
